--- a/docs/deliverables/06_リリース/リリース手順書.xlsx
+++ b/docs/deliverables/06_リリース/リリース手順書.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="文書管理" sheetId="1" r:id="R7d4611eb3ca14a30"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="前提" sheetId="2" r:id="R49908b82373e4be0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="リリース判定" sheetId="3" r:id="Re4657a1afcd64286"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="初回リリース" sheetId="4" r:id="Rec289c5301df4de7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新リリース" sheetId="5" r:id="R7fc4833fd7a340fb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ロールバック" sheetId="6" r:id="R39ec297441d8455f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="リリース後確認" sheetId="7" r:id="R3395529f1774474f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="文書管理" sheetId="1" r:id="R7757284e9f484341"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="前提" sheetId="2" r:id="Rb1254df539d7433a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="リリース判定" sheetId="3" r:id="R3b8ab67721fa43c0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="初回リリース" sheetId="4" r:id="R0d1f8048828d41cd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新リリース" sheetId="5" r:id="R79612d3fe1304616"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ロールバック" sheetId="6" r:id="R049d11cd42e042dc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="リリース後確認" sheetId="7" r:id="Rab3430d4c63943b5"/>
   </x:sheets>
 </x:workbook>
 </file>
